--- a/Customer-Purchase-History/export-data/Customer Behavior & Value/Question 01/high_value_customers.xlsx
+++ b/Customer-Purchase-History/export-data/Customer Behavior & Value/Question 01/high_value_customers.xlsx
@@ -16216,7 +16216,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Customer C5180</t>
+          <t>Customer C1988</t>
         </is>
       </c>
       <c r="B832" t="n">
@@ -16226,16 +16226,16 @@
         <v>1537.08</v>
       </c>
       <c r="D832" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E832" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Customer C1988</t>
+          <t>Customer C5180</t>
         </is>
       </c>
       <c r="B833" t="n">
@@ -16245,10 +16245,10 @@
         <v>1537.08</v>
       </c>
       <c r="D833" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E833" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="834">
@@ -19218,7 +19218,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Customer C4690</t>
+          <t>Customer C7896</t>
         </is>
       </c>
       <c r="B990" t="n">
@@ -19228,16 +19228,16 @@
         <v>1169.04</v>
       </c>
       <c r="D990" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E990" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Customer C7896</t>
+          <t>Customer C4690</t>
         </is>
       </c>
       <c r="B991" t="n">
@@ -19247,10 +19247,10 @@
         <v>1169.04</v>
       </c>
       <c r="D991" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E991" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="992">
@@ -20928,7 +20928,7 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>Customer C8794</t>
+          <t>Customer C8777</t>
         </is>
       </c>
       <c r="B1080" t="n">
@@ -20941,13 +20941,13 @@
         <v>5</v>
       </c>
       <c r="E1080" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>Customer C8777</t>
+          <t>Customer C8794</t>
         </is>
       </c>
       <c r="B1081" t="n">
@@ -20960,7 +20960,7 @@
         <v>5</v>
       </c>
       <c r="E1081" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1082">
@@ -30675,7 +30675,7 @@
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>Customer C6675</t>
+          <t>Customer C1785</t>
         </is>
       </c>
       <c r="B1593" t="n">
@@ -30685,7 +30685,7 @@
         <v>77.69999999999999</v>
       </c>
       <c r="D1593" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1593" t="n">
         <v>5</v>
@@ -30694,7 +30694,7 @@
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>Customer C1785</t>
+          <t>Customer C6675</t>
         </is>
       </c>
       <c r="B1594" t="n">
@@ -30704,7 +30704,7 @@
         <v>77.69999999999999</v>
       </c>
       <c r="D1594" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1594" t="n">
         <v>5</v>
